--- a/public/system/export/nest.xlsx
+++ b/public/system/export/nest.xlsx
@@ -1,94 +1,113 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView xWindow="240" yWindow="570" windowWidth="24615" windowHeight="11955"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="5. Mẫu Nhập Tổ" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="124519"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="SrwXuWqJ7CkLFkkhXZtH0rzSyCMay1WqRegi62f0dY8="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="lDT5JqXZt4NKODR45x6Wo13oR1bg0vRusL1x2CP3qp8="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>STT</t>
+  </si>
+  <si>
+    <t>SỞ GD&amp;ĐT ...</t>
+  </si>
+  <si>
+    <t>CỘNG HÒA XÃ HỘI CHỦ NGHĨA VIỆT NAM</t>
+  </si>
+  <si>
+    <t>TRƯỜNG …</t>
+  </si>
+  <si>
+    <t>Độc lập - Tự do - Hạnh phúc</t>
+  </si>
+  <si>
+    <t>Ngày xuất:</t>
   </si>
   <si>
     <t>Tên</t>
   </si>
   <si>
-    <t>Toán-Trải nghiệm</t>
-  </si>
-  <si>
-    <t>Vật Lý-Trải nghiệm</t>
-  </si>
-  <si>
-    <t>Hóa</t>
-  </si>
-  <si>
-    <t>Sử</t>
-  </si>
-  <si>
-    <t>Địa</t>
-  </si>
-  <si>
-    <t>Tin-Công nghệ</t>
-  </si>
-  <si>
-    <t>Hóa - Sinh</t>
-  </si>
-  <si>
-    <t>Tiếng Anh - Nghệ Thuật</t>
-  </si>
-  <si>
-    <t>Văn - Trải nghiệm</t>
-  </si>
-  <si>
-    <t>Khoa học Xã hội</t>
-  </si>
-  <si>
-    <t>Thể dục - Quốc phòng-AN</t>
-  </si>
-  <si>
-    <t>Văn Phòng</t>
+    <t>DANH SÁCH TỔ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="9">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -97,44 +116,200 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
-    <border/>
+  <borders count="9">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+  <cellXfs count="23">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -324,146 +499,193 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <dimension ref="A1:E1008"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="12.63"/>
-    <col customWidth="1" min="2" max="2" width="34.25"/>
-    <col customWidth="1" min="3" max="3" width="12.63"/>
+    <col min="1" max="1" width="5.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" customWidth="1"/>
+    <col min="3" max="3" width="16.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" ht="15" customHeight="1">
+      <c r="A1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="12"/>
+    </row>
+    <row r="2" spans="1:5" ht="15" customHeight="1">
+      <c r="A2" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="9"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="12"/>
+    </row>
+    <row r="3" spans="1:5" ht="15" customHeight="1">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:5" ht="25.5" customHeight="1">
+      <c r="A4" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+    </row>
+    <row r="5" spans="1:5" ht="15" customHeight="1">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="1:5" ht="15" customHeight="1">
+      <c r="A6" s="1"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="5"/>
+    </row>
+    <row r="9" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A9" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B9" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="18"/>
+    </row>
+    <row r="10" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A10" s="6">
         <v>1</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="3"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="21"/>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="B2" s="4" t="s">
+    <row r="11" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A11" s="7">
         <v>2</v>
       </c>
+      <c r="B11" s="19"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="21"/>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="B3" s="4" t="s">
+    <row r="12" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A12" s="7">
         <v>3</v>
       </c>
+      <c r="B12" s="22"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="21"/>
     </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="B4" s="4" t="s">
+    <row r="13" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A13" s="7">
         <v>4</v>
       </c>
+      <c r="B13" s="22"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="21"/>
     </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="B5" s="4" t="s">
+    <row r="14" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A14" s="7">
         <v>5</v>
       </c>
+      <c r="B14" s="22"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="21"/>
     </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="B6" s="4" t="s">
+    <row r="15" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A15" s="7">
         <v>6</v>
       </c>
+      <c r="B15" s="22"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="21"/>
     </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="B7" s="4" t="s">
+    <row r="16" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A16" s="7">
         <v>7</v>
       </c>
+      <c r="B16" s="22"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="21"/>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="4">
-        <v>7.0</v>
-      </c>
-      <c r="B8" s="5" t="s">
+    <row r="17" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A17" s="7">
         <v>8</v>
       </c>
+      <c r="B17" s="22"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="21"/>
     </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="4">
-        <v>8.0</v>
-      </c>
-      <c r="B9" s="4" t="s">
+    <row r="18" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A18" s="7">
         <v>9</v>
       </c>
+      <c r="B18" s="22"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="21"/>
     </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="4">
-        <v>9.0</v>
-      </c>
-      <c r="B10" s="4" t="s">
+    <row r="19" spans="1:5" ht="15.75" customHeight="1">
+      <c r="A19" s="7">
         <v>10</v>
       </c>
+      <c r="B19" s="13"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="15"/>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="4">
-        <v>10.0</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="5">
-        <v>11.0</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="5">
-        <v>12.0</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" ht="15.75" customHeight="1"/>
-    <row r="15" ht="15.75" customHeight="1"/>
-    <row r="16" ht="15.75" customHeight="1"/>
-    <row r="17" ht="15.75" customHeight="1"/>
-    <row r="18" ht="15.75" customHeight="1"/>
-    <row r="19" ht="15.75" customHeight="1"/>
-    <row r="20" ht="15.75" customHeight="1"/>
-    <row r="21" ht="15.75" customHeight="1"/>
-    <row r="22" ht="15.75" customHeight="1"/>
-    <row r="23" ht="15.75" customHeight="1"/>
-    <row r="24" ht="15.75" customHeight="1"/>
-    <row r="25" ht="15.75" customHeight="1"/>
-    <row r="26" ht="15.75" customHeight="1"/>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="20" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="21" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="22" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="23" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="24" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="25" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="26" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="27" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="28" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="29" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="30" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="31" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="32" spans="1:5" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>
@@ -1432,7 +1654,34 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
+    <row r="1002" ht="15.75" customHeight="1"/>
+    <row r="1003" ht="15.75" customHeight="1"/>
+    <row r="1004" ht="15.75" customHeight="1"/>
+    <row r="1005" ht="15.75" customHeight="1"/>
+    <row r="1006" ht="15.75" customHeight="1"/>
+    <row r="1007" ht="15.75" customHeight="1"/>
+    <row r="1008" ht="15.75" customHeight="1"/>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <mergeCells count="16">
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="D2:E2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>